--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0005_ses-01_pet_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0005_ses-01_pet_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -357,7 +358,7 @@
         <v>0.012322858903265557</v>
       </c>
       <c r="BH1" s="0">
-        <v>0.022311468094600623</v>
+        <v>0.022311468094600624</v>
       </c>
       <c r="BI1" s="0">
         <v>0.010758472296933835</v>
@@ -716,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="BG2" s="0">
-        <v>0.018484288354898334</v>
+        <v>0.018484288354898335</v>
       </c>
       <c r="BH2" s="0">
         <v>0.0055778670236501559</v>
@@ -812,7 +813,7 @@
         <v>0</v>
       </c>
       <c r="CM2" s="0">
-        <v>0.018632383081796162</v>
+        <v>0.018632383081796163</v>
       </c>
       <c r="CN2" s="0">
         <v>0.035893754486719311</v>
@@ -821,7 +822,7 @@
         <v>0</v>
       </c>
       <c r="CP2" s="0">
-        <v>0.0039972818483431267</v>
+        <v>0.0039972818483431268</v>
       </c>
       <c r="CQ2" s="0">
         <v>0</v>
@@ -1051,7 +1052,7 @@
         <v>0.026910656620021532</v>
       </c>
       <c r="AX3" s="0">
-        <v>0.060771801883925856</v>
+        <v>0.060771801883925857</v>
       </c>
       <c r="AY3" s="0">
         <v>0.040444893832153689</v>
@@ -1174,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="CM3" s="0">
-        <v>0.018632383081796162</v>
+        <v>0.018632383081796163</v>
       </c>
       <c r="CN3" s="0">
         <v>0.059822924144532184</v>
@@ -1440,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="BG4" s="0">
-        <v>0.018484288354898334</v>
+        <v>0.018484288354898335</v>
       </c>
       <c r="BH4" s="0">
         <v>0.0055778670236501559</v>
@@ -1802,7 +1803,7 @@
         <v>0</v>
       </c>
       <c r="BG5" s="0">
-        <v>0.018484288354898334</v>
+        <v>0.018484288354898335</v>
       </c>
       <c r="BH5" s="0">
         <v>0.016733601070950468</v>
@@ -1898,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="CM5" s="0">
-        <v>0.018632383081796162</v>
+        <v>0.018632383081796163</v>
       </c>
       <c r="CN5" s="0">
         <v>0.035893754486719311</v>
@@ -2209,7 +2210,7 @@
         <v>0.041446482229820746</v>
       </c>
       <c r="BV6" s="0">
-        <v>0.16380016380016379</v>
+        <v>0.1638001638001638</v>
       </c>
       <c r="BW6" s="0">
         <v>0.043859649122807015</v>
@@ -2373,7 +2374,7 @@
         <v>0.040064102564102567</v>
       </c>
       <c r="H7" s="0">
-        <v>0.020183671409829448</v>
+        <v>0.020183671409829449</v>
       </c>
       <c r="I7" s="0">
         <v>0.011074197120708749</v>
@@ -2496,7 +2497,7 @@
         <v>0.0447127207690588</v>
       </c>
       <c r="AW7" s="0">
-        <v>0.062791532113383577</v>
+        <v>0.062791532113383578</v>
       </c>
       <c r="AX7" s="0">
         <v>0.070900435531246836</v>
@@ -2562,7 +2563,7 @@
         <v>0.12109469605231292</v>
       </c>
       <c r="BS7" s="0">
-        <v>0.080778706732905214</v>
+        <v>0.080778706732905215</v>
       </c>
       <c r="BT7" s="0">
         <v>0.0042398032731281272</v>
@@ -2571,7 +2572,7 @@
         <v>0.072531343902186296</v>
       </c>
       <c r="BV7" s="0">
-        <v>0.16380016380016379</v>
+        <v>0.1638001638001638</v>
       </c>
       <c r="BW7" s="0">
         <v>0.043859649122807015</v>
@@ -2622,7 +2623,7 @@
         <v>0.0063155235569028675</v>
       </c>
       <c r="CM7" s="0">
-        <v>0.13042668157257314</v>
+        <v>0.13042668157257315</v>
       </c>
       <c r="CN7" s="0">
         <v>0.25125628140703515</v>
@@ -2631,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="CP7" s="0">
-        <v>0.0039972818483431267</v>
+        <v>0.0039972818483431268</v>
       </c>
       <c r="CQ7" s="0">
         <v>0</v>
@@ -2924,7 +2925,7 @@
         <v>0.096875756841850333</v>
       </c>
       <c r="BS8" s="0">
-        <v>0.080778706732905214</v>
+        <v>0.080778706732905215</v>
       </c>
       <c r="BT8" s="0">
         <v>0.016959213092512509</v>
@@ -2975,7 +2976,7 @@
         <v>0</v>
       </c>
       <c r="CJ8" s="0">
-        <v>0.094876660341555979</v>
+        <v>0.09487666034155598</v>
       </c>
       <c r="CK8" s="0">
         <v>0.056761742585497377</v>
@@ -3115,7 +3116,7 @@
         <v>0.055440055440055397</v>
       </c>
       <c r="N9" s="0">
-        <v>0.041536863966770476</v>
+        <v>0.041536863966770477</v>
       </c>
       <c r="O9" s="0">
         <v>0.013183046602069728</v>
@@ -3184,7 +3185,7 @@
         <v>0.16511867905056746</v>
       </c>
       <c r="AK9" s="0">
-        <v>0.059430948666518039</v>
+        <v>0.05943094866651804</v>
       </c>
       <c r="AL9" s="0">
         <v>0.025794802347326989</v>
@@ -3298,7 +3299,7 @@
         <v>0.11466011466011455</v>
       </c>
       <c r="BW9" s="0">
-        <v>0.04385964912280698</v>
+        <v>0.043859649122806981</v>
       </c>
       <c r="BX9" s="0">
         <v>0.02804655728509323</v>
@@ -3495,7 +3496,7 @@
         <v>0.060369647998514041</v>
       </c>
       <c r="T10" s="0">
-        <v>0.034146008331626065</v>
+        <v>0.034146008331626066</v>
       </c>
       <c r="U10" s="0">
         <v>0.018590816136828427</v>
@@ -3528,7 +3529,7 @@
         <v>0.1903402331667858</v>
       </c>
       <c r="AE10" s="0">
-        <v>0.068306010928961824</v>
+        <v>0.068306010928961825</v>
       </c>
       <c r="AF10" s="0">
         <v>0.070175438596491294</v>
@@ -3603,7 +3604,7 @@
         <v>0.0042322668020992084</v>
       </c>
       <c r="BD10" s="0">
-        <v>0.034258307639602636</v>
+        <v>0.034258307639602637</v>
       </c>
       <c r="BE10" s="0">
         <v>0.015627441787779358</v>
@@ -3624,7 +3625,7 @@
         <v>0.036852773171181165</v>
       </c>
       <c r="BK10" s="0">
-        <v>0.020605810838656521</v>
+        <v>0.020605810838656522</v>
       </c>
       <c r="BL10" s="0">
         <v>0.0127372309259967</v>
@@ -3699,7 +3700,7 @@
         <v>0.011092623405435396</v>
       </c>
       <c r="CJ10" s="0">
-        <v>0.26354627872654462</v>
+        <v>0.26354627872654463</v>
       </c>
       <c r="CK10" s="0">
         <v>0.056761742585497432</v>
@@ -3711,7 +3712,7 @@
         <v>0.14905906465436944</v>
       </c>
       <c r="CN10" s="0">
-        <v>0.19143335726250318</v>
+        <v>0.19143335726250319</v>
       </c>
       <c r="CO10" s="0">
         <v>0.030856034558758735</v>
@@ -3821,7 +3822,7 @@
         <v>0.080128205128205066</v>
       </c>
       <c r="H11" s="0">
-        <v>0.050459178524573572</v>
+        <v>0.050459178524573573</v>
       </c>
       <c r="I11" s="0">
         <v>0.071982281284606806</v>
@@ -3866,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="W11" s="0">
-        <v>0.085470085470085388</v>
+        <v>0.085470085470085389</v>
       </c>
       <c r="X11" s="0">
         <v>0.03790032215273826</v>
@@ -3908,7 +3909,7 @@
         <v>0.26831785345717207</v>
       </c>
       <c r="AK11" s="0">
-        <v>0.059430948666518039</v>
+        <v>0.05943094866651804</v>
       </c>
       <c r="AL11" s="0">
         <v>0.070935706455149225</v>
@@ -3947,7 +3948,7 @@
         <v>0.12558306422676702</v>
       </c>
       <c r="AX11" s="0">
-        <v>0.41527397954015965</v>
+        <v>0.41527397954015966</v>
       </c>
       <c r="AY11" s="0">
         <v>0.31007751937984468</v>
@@ -4037,7 +4038,7 @@
         <v>0</v>
       </c>
       <c r="CB11" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC11" s="0">
         <v>0.062492188476440391</v>
@@ -4064,7 +4065,7 @@
         <v>0.2108370229812353</v>
       </c>
       <c r="CK11" s="0">
-        <v>0.087980701007520853</v>
+        <v>0.087980701007520854</v>
       </c>
       <c r="CL11" s="0">
         <v>0.0031577617784514307</v>
@@ -4177,7 +4178,7 @@
         <v>0.087219262997227751</v>
       </c>
       <c r="F12" s="0">
-        <v>0.054517804367163115</v>
+        <v>0.054517804367163116</v>
       </c>
       <c r="G12" s="0">
         <v>0.093482905982906067</v>
@@ -4216,7 +4217,7 @@
         <v>0.045913682277318686</v>
       </c>
       <c r="S12" s="0">
-        <v>0.037150552614470179</v>
+        <v>0.03715055261447018</v>
       </c>
       <c r="T12" s="0">
         <v>0.088779621662227776</v>
@@ -4228,7 +4229,7 @@
         <v>0</v>
       </c>
       <c r="W12" s="0">
-        <v>0.068376068376068438</v>
+        <v>0.068376068376068439</v>
       </c>
       <c r="X12" s="0">
         <v>0</v>
@@ -4249,10 +4250,10 @@
         <v>0.14184397163120582</v>
       </c>
       <c r="AD12" s="0">
-        <v>0.40447299547941989</v>
+        <v>0.4044729954794199</v>
       </c>
       <c r="AE12" s="0">
-        <v>0.068306010928961824</v>
+        <v>0.068306010928961825</v>
       </c>
       <c r="AF12" s="0">
         <v>0.21052631578947389</v>
@@ -4294,7 +4295,7 @@
         <v>0.049844236760124658</v>
       </c>
       <c r="AS12" s="0">
-        <v>0.33068783068783097</v>
+        <v>0.33068783068783098</v>
       </c>
       <c r="AT12" s="0">
         <v>0.11129660545353377</v>
@@ -4342,10 +4343,10 @@
         <v>0.066934404283801929</v>
       </c>
       <c r="BI12" s="0">
-        <v>0.20082481620943179</v>
+        <v>0.2008248162094318</v>
       </c>
       <c r="BJ12" s="0">
-        <v>0.088446655610834798</v>
+        <v>0.088446655610834799</v>
       </c>
       <c r="BK12" s="0">
         <v>0.027474414451542029</v>
@@ -4390,7 +4391,7 @@
         <v>0.070116393212733205</v>
       </c>
       <c r="BY12" s="0">
-        <v>0.069676700111482789</v>
+        <v>0.06967670011148279</v>
       </c>
       <c r="BZ12" s="0">
         <v>0.11848341232227499</v>
@@ -4530,13 +4531,13 @@
         <v>0.13798294029101846</v>
       </c>
       <c r="C13" s="0">
-        <v>0.23272941523051976</v>
+        <v>0.23272941523051977</v>
       </c>
       <c r="D13" s="0">
         <v>0.092888561046908638</v>
       </c>
       <c r="E13" s="0">
-        <v>0.065414447247920698</v>
+        <v>0.065414447247920699</v>
       </c>
       <c r="F13" s="0">
         <v>0.074603311239275702</v>
@@ -4605,7 +4606,7 @@
         <v>0.11726766344180582</v>
       </c>
       <c r="AB13" s="0">
-        <v>0.20437359493153467</v>
+        <v>0.20437359493153468</v>
       </c>
       <c r="AC13" s="0">
         <v>0.094562647754137044</v>
@@ -4626,7 +4627,7 @@
         <v>0.15857913098636206</v>
       </c>
       <c r="AI13" s="0">
-        <v>0.34458295327860516</v>
+        <v>0.34458295327860517</v>
       </c>
       <c r="AJ13" s="0">
         <v>0.3921568627450977</v>
@@ -4662,7 +4663,7 @@
         <v>0.055648302726766789</v>
       </c>
       <c r="AU13" s="0">
-        <v>0.037091988130563767</v>
+        <v>0.037091988130563768</v>
       </c>
       <c r="AV13" s="0">
         <v>0.23101572397347026</v>
@@ -4761,10 +4762,10 @@
         <v>0</v>
       </c>
       <c r="CB13" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC13" s="0">
-        <v>0.074990626171728469</v>
+        <v>0.07499062617172847</v>
       </c>
       <c r="CD13" s="0">
         <v>0.01282051282051281</v>
@@ -4800,7 +4801,7 @@
         <v>0.34697296003828637</v>
       </c>
       <c r="CO13" s="0">
-        <v>0.070528078991448417</v>
+        <v>0.070528078991448418</v>
       </c>
       <c r="CP13" s="0">
         <v>0.059959227725146849</v>
@@ -4937,7 +4938,7 @@
         <v>0.15432098765432112</v>
       </c>
       <c r="R14" s="0">
-        <v>0.18365472910927474</v>
+        <v>0.18365472910927475</v>
       </c>
       <c r="S14" s="0">
         <v>0.11609547692021931</v>
@@ -4976,10 +4977,10 @@
         <v>0.38068046633357161</v>
       </c>
       <c r="AE14" s="0">
-        <v>0.068306010928961824</v>
+        <v>0.068306010928961825</v>
       </c>
       <c r="AF14" s="0">
-        <v>0.28070175438596517</v>
+        <v>0.28070175438596518</v>
       </c>
       <c r="AG14" s="0">
         <v>0.0075448921080428621</v>
@@ -5024,7 +5025,7 @@
         <v>0.11129660545353377</v>
       </c>
       <c r="AU14" s="0">
-        <v>0.018545994065281918</v>
+        <v>0.018545994065281919</v>
       </c>
       <c r="AV14" s="0">
         <v>0.26827632461435308</v>
@@ -5042,7 +5043,7 @@
         <v>0.012350253180190205</v>
       </c>
       <c r="BA14" s="0">
-        <v>0.49281744783474934</v>
+        <v>0.49281744783474935</v>
       </c>
       <c r="BB14" s="0">
         <v>0.11827321111768196</v>
@@ -5105,7 +5106,7 @@
         <v>0.31084861672365588</v>
       </c>
       <c r="BV14" s="0">
-        <v>0.42588042588042629</v>
+        <v>0.4258804258804263</v>
       </c>
       <c r="BW14" s="0">
         <v>0.13157894736842118</v>
@@ -5117,7 +5118,7 @@
         <v>0.20903010033444835</v>
       </c>
       <c r="BZ14" s="0">
-        <v>0.17114270668773054</v>
+        <v>0.17114270668773055</v>
       </c>
       <c r="CA14" s="0">
         <v>0</v>
@@ -5147,7 +5148,7 @@
         <v>0.066555740432612379</v>
       </c>
       <c r="CJ14" s="0">
-        <v>0.33733923676997712</v>
+        <v>0.33733923676997713</v>
       </c>
       <c r="CK14" s="0">
         <v>0.15041861785156818</v>
@@ -5251,7 +5252,7 @@
         <v>0.15698587127158539</v>
       </c>
       <c r="B15" s="0">
-        <v>0.17561465127947803</v>
+        <v>0.17561465127947804</v>
       </c>
       <c r="C15" s="0">
         <v>0.29164825452938553</v>
@@ -5290,7 +5291,7 @@
         <v>0.13499480789200405</v>
       </c>
       <c r="O15" s="0">
-        <v>0.098872849515522956</v>
+        <v>0.098872849515522957</v>
       </c>
       <c r="P15" s="0">
         <v>0.10237160894045376</v>
@@ -5326,10 +5327,10 @@
         <v>0.1830244795241362</v>
       </c>
       <c r="AA15" s="0">
-        <v>0.23453532688361164</v>
+        <v>0.23453532688361165</v>
       </c>
       <c r="AB15" s="0">
-        <v>0.20437359493153467</v>
+        <v>0.20437359493153468</v>
       </c>
       <c r="AC15" s="0">
         <v>0.18912529550827409</v>
@@ -5458,7 +5459,7 @@
         <v>0.33906514894647583</v>
       </c>
       <c r="BS15" s="0">
-        <v>0.29080334423845849</v>
+        <v>0.2908033442384585</v>
       </c>
       <c r="BT15" s="0">
         <v>0.076316458916306215</v>
@@ -5485,7 +5486,7 @@
         <v>0</v>
       </c>
       <c r="CB15" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC15" s="0">
         <v>0.049993750781152313</v>
@@ -5506,7 +5507,7 @@
         <v>0.11041915109756625</v>
       </c>
       <c r="CI15" s="0">
-        <v>0.044370493621741502</v>
+        <v>0.044370493621741503</v>
       </c>
       <c r="CJ15" s="0">
         <v>0.3057136833227912</v>
@@ -5613,7 +5614,7 @@
         <v>0.22541561003099486</v>
       </c>
       <c r="B16" s="0">
-        <v>0.1923398561632382</v>
+        <v>0.19233985616323821</v>
       </c>
       <c r="C16" s="0">
         <v>0.29459419649432933</v>
@@ -5700,7 +5701,7 @@
         <v>0.66619081608375041</v>
       </c>
       <c r="AE16" s="0">
-        <v>0.068306010928961824</v>
+        <v>0.068306010928961825</v>
       </c>
       <c r="AF16" s="0">
         <v>0.35087719298245645</v>
@@ -5766,7 +5767,7 @@
         <v>0.018525379770285309</v>
       </c>
       <c r="BA16" s="0">
-        <v>0.58718674635629708</v>
+        <v>0.58718674635629709</v>
       </c>
       <c r="BB16" s="0">
         <v>0.31539522964715194</v>
@@ -5802,7 +5803,7 @@
         <v>0.0254744618519934</v>
       </c>
       <c r="BM16" s="0">
-        <v>0.046352627614577951</v>
+        <v>0.046352627614577952</v>
       </c>
       <c r="BN16" s="0">
         <v>0.2897650833074617</v>
@@ -5934,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="DE16" s="0">
-        <v>0.048332527791203519</v>
+        <v>0.04833252779120352</v>
       </c>
       <c r="DF16" s="0">
         <v>0</v>
@@ -6248,7 +6249,7 @@
         <v>0.52644173247188275</v>
       </c>
       <c r="CO17" s="0">
-        <v>0.070528078991448417</v>
+        <v>0.070528078991448418</v>
       </c>
       <c r="CP17" s="0">
         <v>0.083942918815205589</v>
@@ -6346,10 +6347,10 @@
         <v>0.28139769964210559</v>
       </c>
       <c r="E18" s="0">
-        <v>0.23985297324237589</v>
+        <v>0.2398529732423759</v>
       </c>
       <c r="F18" s="0">
-        <v>0.19798571059653935</v>
+        <v>0.19798571059653936</v>
       </c>
       <c r="G18" s="0">
         <v>0.253739316239316</v>
@@ -6361,7 +6362,7 @@
         <v>0.26578073089700971</v>
       </c>
       <c r="J18" s="0">
-        <v>0.31971353667114238</v>
+        <v>0.31971353667114239</v>
       </c>
       <c r="K18" s="0">
         <v>0.22805017103762809</v>
@@ -6376,7 +6377,7 @@
         <v>0.2699896157840081</v>
       </c>
       <c r="O18" s="0">
-        <v>0.20433722233208076</v>
+        <v>0.20433722233208077</v>
       </c>
       <c r="P18" s="0">
         <v>0.1251208553716657</v>
@@ -6574,7 +6575,7 @@
         <v>0.4199475065616794</v>
       </c>
       <c r="CC18" s="0">
-        <v>0.24996875390576156</v>
+        <v>0.24996875390576157</v>
       </c>
       <c r="CD18" s="0">
         <v>0.076923076923076858</v>
@@ -6786,7 +6787,7 @@
         <v>1.0944563407090204</v>
       </c>
       <c r="AE19" s="0">
-        <v>0.54644808743169559</v>
+        <v>0.5464480874316956</v>
       </c>
       <c r="AF19" s="0">
         <v>0.28070175438596567</v>
@@ -6819,7 +6820,7 @@
         <v>0.22471910112359614</v>
       </c>
       <c r="AP19" s="0">
-        <v>0.88300220750552127</v>
+        <v>0.88300220750552128</v>
       </c>
       <c r="AQ19" s="0">
         <v>0.10014306151645236</v>
@@ -6837,7 +6838,7 @@
         <v>0.12363996043521301</v>
       </c>
       <c r="AV19" s="0">
-        <v>0.52164840897235409</v>
+        <v>0.5216484089723541</v>
       </c>
       <c r="AW19" s="0">
         <v>0.47542160028704833</v>
@@ -7181,7 +7182,7 @@
         <v>0.41947565543071125</v>
       </c>
       <c r="AP20" s="0">
-        <v>0.85356880058866746</v>
+        <v>0.85356880058866747</v>
       </c>
       <c r="AQ20" s="0">
         <v>0.18597997138769654</v>
@@ -7208,13 +7209,13 @@
         <v>0.87106249366960309</v>
       </c>
       <c r="AY20" s="0">
-        <v>0.82237950792045766</v>
+        <v>0.82237950792045767</v>
       </c>
       <c r="AZ20" s="0">
         <v>0.04940101272076073</v>
       </c>
       <c r="BA20" s="0">
-        <v>0.89126559714794928</v>
+        <v>0.89126559714794929</v>
       </c>
       <c r="BB20" s="0">
         <v>0.54208555095604127</v>
@@ -7504,7 +7505,7 @@
         <v>0.40874718986306935</v>
       </c>
       <c r="AC21" s="0">
-        <v>0.59101654846335649</v>
+        <v>0.5910165484633565</v>
       </c>
       <c r="AD21" s="0">
         <v>1.3561741613133464</v>
@@ -7555,7 +7556,7 @@
         <v>0.66137566137566073</v>
       </c>
       <c r="AT21" s="0">
-        <v>0.44518642181413431</v>
+        <v>0.44518642181413432</v>
       </c>
       <c r="AU21" s="0">
         <v>0.098911968348170051</v>
@@ -7600,7 +7601,7 @@
         <v>0.3848728246318604</v>
       </c>
       <c r="BI21" s="0">
-        <v>0.64550833781602956</v>
+        <v>0.64550833781602957</v>
       </c>
       <c r="BJ21" s="0">
         <v>0.4090657822001102</v>
@@ -7627,7 +7628,7 @@
         <v>0.3110792055515671</v>
       </c>
       <c r="BR21" s="0">
-        <v>0.80729797368208533</v>
+        <v>0.80729797368208534</v>
       </c>
       <c r="BS21" s="0">
         <v>0.61795710650672431</v>
@@ -7660,7 +7661,7 @@
         <v>0.4199475065616794</v>
       </c>
       <c r="CC21" s="0">
-        <v>0.32495938007749003</v>
+        <v>0.32495938007749004</v>
       </c>
       <c r="CD21" s="0">
         <v>0.10256410256410248</v>
@@ -7681,7 +7682,7 @@
         <v>0.22185246810870751</v>
       </c>
       <c r="CJ21" s="0">
-        <v>0.71684587813620015</v>
+        <v>0.71684587813620016</v>
       </c>
       <c r="CK21" s="0">
         <v>0.51653185752802566</v>
@@ -7854,7 +7855,7 @@
         <v>0.22740193291642957</v>
       </c>
       <c r="Y22" s="0">
-        <v>0.44549266247379415</v>
+        <v>0.44549266247379416</v>
       </c>
       <c r="Z22" s="0">
         <v>0.8236101578586128</v>
@@ -7869,7 +7870,7 @@
         <v>0.75650118203309635</v>
       </c>
       <c r="AD22" s="0">
-        <v>1.0706638115631681</v>
+        <v>1.0706638115631682</v>
       </c>
       <c r="AE22" s="0">
         <v>0.47814207650273183</v>
@@ -7977,7 +7978,7 @@
         <v>0.28390984413928944</v>
       </c>
       <c r="BN22" s="0">
-        <v>0.66232019041705414</v>
+        <v>0.66232019041705415</v>
       </c>
       <c r="BO22" s="0">
         <v>0.12383203872565564</v>
@@ -8147,7 +8148,7 @@
         <v>0.60781709133357653</v>
       </c>
       <c r="B23" s="0">
-        <v>0.68155209901321478</v>
+        <v>0.68155209901321479</v>
       </c>
       <c r="C23" s="0">
         <v>0.80718809839446393</v>
@@ -8231,7 +8232,7 @@
         <v>0.56737588652482429</v>
       </c>
       <c r="AD23" s="0">
-        <v>1.0706638115631721</v>
+        <v>1.0706638115631722</v>
       </c>
       <c r="AE23" s="0">
         <v>0.7513661202185814</v>
@@ -8252,7 +8253,7 @@
         <v>1.0939112487100136</v>
       </c>
       <c r="AK23" s="0">
-        <v>0.69831364683158947</v>
+        <v>0.69831364683158948</v>
       </c>
       <c r="AL23" s="0">
         <v>0.58683175340169125</v>
@@ -8273,7 +8274,7 @@
         <v>0.25751072961373461</v>
       </c>
       <c r="AR23" s="0">
-        <v>0.14953271028037426</v>
+        <v>0.14953271028037427</v>
       </c>
       <c r="AS23" s="0">
         <v>0.52910052910053051</v>
@@ -8351,10 +8352,10 @@
         <v>0.35893754486719415</v>
       </c>
       <c r="BR23" s="0">
-        <v>0.87995479131347631</v>
+        <v>0.87995479131347632</v>
       </c>
       <c r="BS23" s="0">
-        <v>0.81990387333899017</v>
+        <v>0.81990387333899018</v>
       </c>
       <c r="BT23" s="0">
         <v>0.36886288476214812</v>
@@ -8474,7 +8475,7 @@
         <v>0.10224948875255653</v>
       </c>
       <c r="DG23" s="0">
-        <v>0.50813008130081438</v>
+        <v>0.50813008130081439</v>
       </c>
       <c r="DH23" s="0">
         <v>0</v>
@@ -8590,7 +8591,7 @@
         <v>0.8174943797261387</v>
       </c>
       <c r="AC24" s="0">
-        <v>0.78014184397163044</v>
+        <v>0.78014184397163045</v>
       </c>
       <c r="AD24" s="0">
         <v>1.2372115155841055</v>
@@ -8692,7 +8693,7 @@
         <v>0.69283213561820467</v>
       </c>
       <c r="BK24" s="0">
-        <v>0.41898482038601514</v>
+        <v>0.41898482038601515</v>
       </c>
       <c r="BL24" s="0">
         <v>0.24837600305693519</v>
@@ -8734,7 +8735,7 @@
         <v>0.33655868742111872</v>
       </c>
       <c r="BY24" s="0">
-        <v>0.85005574136008843</v>
+        <v>0.85005574136008844</v>
       </c>
       <c r="BZ24" s="0">
         <v>0.84254870984728725</v>
@@ -8770,7 +8771,7 @@
         <v>0.96985030571368247</v>
       </c>
       <c r="CK24" s="0">
-        <v>0.66127430112104379</v>
+        <v>0.6612743011210438</v>
       </c>
       <c r="CL24" s="0">
         <v>0.13262599469496009</v>
@@ -9051,7 +9052,7 @@
         <v>0.9144701452393752</v>
       </c>
       <c r="BJ25" s="0">
-        <v>0.71862907683803134</v>
+        <v>0.71862907683803135</v>
       </c>
       <c r="BK25" s="0">
         <v>0.46706504567621365</v>
@@ -9060,7 +9061,7 @@
         <v>0.30569354222392026</v>
       </c>
       <c r="BM25" s="0">
-        <v>0.35343878556115615</v>
+        <v>0.35343878556115616</v>
       </c>
       <c r="BN25" s="0">
         <v>1.0038290386008477</v>
@@ -9087,7 +9088,7 @@
         <v>0.9843539529582418</v>
       </c>
       <c r="BV25" s="0">
-        <v>0.93366093366093283</v>
+        <v>0.93366093366093284</v>
       </c>
       <c r="BW25" s="0">
         <v>0.71637426900584733</v>
@@ -9102,7 +9103,7 @@
         <v>0.84254870984728725</v>
       </c>
       <c r="CA25" s="0">
-        <v>0.25062656641603986</v>
+        <v>0.25062656641603987</v>
       </c>
       <c r="CB25" s="0">
         <v>0.89238845144356871</v>
@@ -9129,7 +9130,7 @@
         <v>0.4991680532445919</v>
       </c>
       <c r="CJ25" s="0">
-        <v>1.3388150959308442</v>
+        <v>1.3388150959308443</v>
       </c>
       <c r="CK25" s="0">
         <v>0.80317865758478713</v>
@@ -9138,7 +9139,7 @@
         <v>0.19578123026398872</v>
       </c>
       <c r="CM25" s="0">
-        <v>0.96888392025339964</v>
+        <v>0.96888392025339965</v>
       </c>
       <c r="CN25" s="0">
         <v>1.1725293132328298</v>
@@ -9236,7 +9237,7 @@
         <v>0.90734236494396969</v>
       </c>
       <c r="C26" s="0">
-        <v>1.0399175136249807</v>
+        <v>1.0399175136249808</v>
       </c>
       <c r="D26" s="0">
         <v>0.75403655438078776</v>
@@ -9305,7 +9306,7 @@
         <v>0.91719077568134089</v>
       </c>
       <c r="Z26" s="0">
-        <v>0.75497597803706173</v>
+        <v>0.75497597803706174</v>
       </c>
       <c r="AA26" s="0">
         <v>0.93814130753444658</v>
@@ -9389,7 +9390,7 @@
         <v>1.2477718360071288</v>
       </c>
       <c r="BB26" s="0">
-        <v>1.0250344963532418</v>
+        <v>1.0250344963532419</v>
       </c>
       <c r="BC26" s="0">
         <v>0.26663280853224963</v>
@@ -9413,7 +9414,7 @@
         <v>0.99336560875022328</v>
       </c>
       <c r="BJ26" s="0">
-        <v>0.87709600147411015</v>
+        <v>0.87709600147411016</v>
       </c>
       <c r="BK26" s="0">
         <v>0.43272202761178619</v>
@@ -9506,7 +9507,7 @@
         <v>1.1725293132328298</v>
       </c>
       <c r="CO26" s="0">
-        <v>0.50692056775103544</v>
+        <v>0.50692056775103545</v>
       </c>
       <c r="CP26" s="0">
         <v>0.47567653995283166</v>
@@ -9616,7 +9617,7 @@
         <v>0.63578564940962712</v>
       </c>
       <c r="I27" s="0">
-        <v>0.78626799557032045</v>
+        <v>0.78626799557032046</v>
       </c>
       <c r="J27" s="0">
         <v>0.81207238314470165</v>
@@ -9634,7 +9635,7 @@
         <v>0.8618899273104873</v>
       </c>
       <c r="O27" s="0">
-        <v>0.62619471359831202</v>
+        <v>0.62619471359831203</v>
       </c>
       <c r="P27" s="0">
         <v>0.65972814650514644</v>
@@ -9649,7 +9650,7 @@
         <v>0.79409306213429853</v>
       </c>
       <c r="T27" s="0">
-        <v>0.69657856996517042</v>
+        <v>0.69657856996517043</v>
       </c>
       <c r="U27" s="0">
         <v>0.29745305818925427</v>
@@ -9694,7 +9695,7 @@
         <v>0.97526165556612665</v>
       </c>
       <c r="AI27" s="0">
-        <v>1.3175230566534903</v>
+        <v>1.3175230566534904</v>
       </c>
       <c r="AJ27" s="0">
         <v>1.351909184726521</v>
@@ -9781,7 +9782,7 @@
         <v>0.54261968541795402</v>
       </c>
       <c r="BL27" s="0">
-        <v>0.44580308240988364</v>
+        <v>0.44580308240988365</v>
       </c>
       <c r="BM27" s="0">
         <v>0.46352627614577863</v>
@@ -9805,7 +9806,7 @@
         <v>1.0178117048346047</v>
       </c>
       <c r="BT27" s="0">
-        <v>0.71652675315865288</v>
+        <v>0.71652675315865289</v>
       </c>
       <c r="BU27" s="0">
         <v>1.1708631229924349</v>
@@ -9901,7 +9902,7 @@
         <v>0.76991652483993778</v>
       </c>
       <c r="CZ27" s="0">
-        <v>0.155363940029519</v>
+        <v>0.15536394002951901</v>
       </c>
       <c r="DA27" s="0">
         <v>0</v>
@@ -10011,7 +10012,7 @@
         <v>0.84053125290238928</v>
       </c>
       <c r="T28" s="0">
-        <v>0.64877415830089646</v>
+        <v>0.64877415830089647</v>
       </c>
       <c r="U28" s="0">
         <v>0.29745305818925538</v>
@@ -10101,7 +10102,7 @@
         <v>1.1123071402942262</v>
       </c>
       <c r="AX28" s="0">
-        <v>1.3572369087410145</v>
+        <v>1.3572369087410146</v>
       </c>
       <c r="AY28" s="0">
         <v>1.2403100775193834</v>
@@ -10131,7 +10132,7 @@
         <v>0.98582871226124735</v>
       </c>
       <c r="BH28" s="0">
-        <v>0.95939312806782961</v>
+        <v>0.95939312806782962</v>
       </c>
       <c r="BI28" s="0">
         <v>1.1583288506365463</v>
@@ -10227,7 +10228,7 @@
         <v>1.1552077510713652</v>
       </c>
       <c r="CN28" s="0">
-        <v>1.2323522373773665</v>
+        <v>1.2323522373773666</v>
       </c>
       <c r="CO28" s="0">
         <v>0.60389667636427924</v>
@@ -10236,7 +10237,7 @@
         <v>0.579605868009755</v>
       </c>
       <c r="CQ28" s="0">
-        <v>3.0613350671868313</v>
+        <v>3.0613350671868314</v>
       </c>
       <c r="CR28" s="0">
         <v>0.085224246298072043</v>
@@ -10281,7 +10282,7 @@
         <v>3.4960528435637284</v>
       </c>
       <c r="DF28" s="0">
-        <v>1.5848670756646261</v>
+        <v>1.5848670756646262</v>
       </c>
       <c r="DG28" s="0">
         <v>3.1504065040650495</v>
@@ -10316,7 +10317,7 @@
     </row>
     <row r="29">
       <c r="A29" s="0">
-        <v>0.92581411262729862</v>
+        <v>0.92581411262729863</v>
       </c>
       <c r="B29" s="0">
         <v>1.0536879076768682</v>
@@ -10334,7 +10335,7 @@
         <v>0.93254139049094631</v>
       </c>
       <c r="G29" s="0">
-        <v>1.282051282051281</v>
+        <v>1.2820512820512811</v>
       </c>
       <c r="H29" s="0">
         <v>0.87798970632758022</v>
@@ -10346,7 +10347,7 @@
         <v>0.97192915148027281</v>
       </c>
       <c r="K29" s="0">
-        <v>0.91220068415051236</v>
+        <v>0.91220068415051237</v>
       </c>
       <c r="L29" s="0">
         <v>0.87018291600070963</v>
@@ -10415,7 +10416,7 @@
         <v>0.39987928172627096</v>
       </c>
       <c r="AH29" s="0">
-        <v>1.2607040913415783</v>
+        <v>1.2607040913415784</v>
       </c>
       <c r="AI29" s="0">
         <v>1.1857707509881414</v>
@@ -10568,10 +10569,10 @@
         <v>0.51813471502590625</v>
       </c>
       <c r="CG29" s="0">
-        <v>0.65000295455888379</v>
+        <v>0.6500029545588838</v>
       </c>
       <c r="CH29" s="0">
-        <v>0.81268495207808777</v>
+        <v>0.81268495207808778</v>
       </c>
       <c r="CI29" s="0">
         <v>0.58790904048807491</v>
@@ -10586,7 +10587,7 @@
         <v>0.37893141341417169</v>
       </c>
       <c r="CM29" s="0">
-        <v>1.3787963480529148</v>
+        <v>1.3787963480529149</v>
       </c>
       <c r="CN29" s="0">
         <v>1.2323522373773621</v>
@@ -10711,7 +10712,7 @@
         <v>1.0832383124287333</v>
       </c>
       <c r="L30" s="0">
-        <v>1.1188066062866266</v>
+        <v>1.1188066062866267</v>
       </c>
       <c r="M30" s="0">
         <v>1.1226611226611218</v>
@@ -10891,7 +10892,7 @@
         <v>1.3651601437860967</v>
       </c>
       <c r="BT30" s="0">
-        <v>0.80980242516747158</v>
+        <v>0.80980242516747159</v>
       </c>
       <c r="BU30" s="0">
         <v>1.3988187752564487</v>
@@ -10969,7 +10970,7 @@
         <v>0.4791390240306645</v>
       </c>
       <c r="CT30" s="0">
-        <v>1.7954879188359349</v>
+        <v>1.795487918835935</v>
       </c>
       <c r="CU30" s="0">
         <v>2.2954091816367246</v>
@@ -11020,7 +11021,7 @@
         <v>0.67750677506775003</v>
       </c>
       <c r="DK30" s="0">
-        <v>2.1729079981507144</v>
+        <v>2.1729079981507145</v>
       </c>
       <c r="DL30" s="0">
         <v>0.47867711053089601</v>
@@ -11040,7 +11041,7 @@
     </row>
     <row r="31">
       <c r="A31" s="0">
-        <v>1.1351286076560791</v>
+        <v>1.1351286076560792</v>
       </c>
       <c r="B31" s="0">
         <v>1.0787757150025077</v>
@@ -11103,7 +11104,7 @@
         <v>0.44617958728388141</v>
       </c>
       <c r="V31" s="0">
-        <v>0.68933823529411697</v>
+        <v>0.68933823529411698</v>
       </c>
       <c r="W31" s="0">
         <v>1.5726495726495713</v>
@@ -11148,7 +11149,7 @@
         <v>1.2383900928792557</v>
       </c>
       <c r="AK31" s="0">
-        <v>1.2034767104969903</v>
+        <v>1.2034767104969904</v>
       </c>
       <c r="AL31" s="0">
         <v>1.2445992132585273</v>
@@ -11241,7 +11242,7 @@
         <v>0.50658561296859128</v>
       </c>
       <c r="BP31" s="0">
-        <v>1.1537330981775415</v>
+        <v>1.1537330981775416</v>
       </c>
       <c r="BQ31" s="0">
         <v>0.89734386216798201</v>
@@ -11268,10 +11269,10 @@
         <v>0.78530360398261045</v>
       </c>
       <c r="BY31" s="0">
-        <v>1.282051282051281</v>
+        <v>1.2820512820512811</v>
       </c>
       <c r="BZ31" s="0">
-        <v>1.0926803580832007</v>
+        <v>1.0926803580832008</v>
       </c>
       <c r="CA31" s="0">
         <v>0.55137844611528763</v>
@@ -11540,7 +11541,7 @@
         <v>1.7250973845297768</v>
       </c>
       <c r="AU32" s="0">
-        <v>0.64910979228486831</v>
+        <v>0.64910979228486832</v>
       </c>
       <c r="AV32" s="0">
         <v>1.2668604217900028</v>
@@ -11702,7 +11703,7 @@
         <v>3.5447761194029952</v>
       </c>
       <c r="CW32" s="0">
-        <v>3.3369736682441546</v>
+        <v>3.3369736682441547</v>
       </c>
       <c r="CX32" s="0">
         <v>3.1639501438159248</v>
@@ -11800,7 +11801,7 @@
         <v>1.2786361214704305</v>
       </c>
       <c r="M33" s="0">
-        <v>1.2612612612612601</v>
+        <v>1.2612612612612602</v>
       </c>
       <c r="N33" s="0">
         <v>1.412253374870196</v>
@@ -11920,7 +11921,7 @@
         <v>0.60516240582931902</v>
       </c>
       <c r="BA33" s="0">
-        <v>0.97514941805599153</v>
+        <v>0.97514941805599154</v>
       </c>
       <c r="BB33" s="0">
         <v>1.2221565148827112</v>
@@ -11941,7 +11942,7 @@
         <v>1.1213801601971647</v>
       </c>
       <c r="BH33" s="0">
-        <v>1.2717536813922345</v>
+        <v>1.2717536813922346</v>
       </c>
       <c r="BI33" s="0">
         <v>1.2838443607674366</v>
@@ -11980,7 +11981,7 @@
         <v>1.1193080641058244</v>
       </c>
       <c r="BU33" s="0">
-        <v>1.1397782613200695</v>
+        <v>1.1397782613200696</v>
       </c>
       <c r="BV33" s="0">
         <v>1.1793611793611785</v>
@@ -11992,7 +11993,7 @@
         <v>1.0938157341186361</v>
       </c>
       <c r="BY33" s="0">
-        <v>1.4492753623188392</v>
+        <v>1.4492753623188393</v>
       </c>
       <c r="BZ33" s="0">
         <v>1.171669299631384</v>
@@ -12007,7 +12008,7 @@
         <v>0.9748781402324701</v>
       </c>
       <c r="CD33" s="0">
-        <v>0.85897435897435825</v>
+        <v>0.85897435897435826</v>
       </c>
       <c r="CE33" s="0">
         <v>1.2063492063492052</v>
@@ -12025,7 +12026,7 @@
         <v>0.93178036605657155</v>
       </c>
       <c r="CJ33" s="0">
-        <v>1.3388150959308442</v>
+        <v>1.3388150959308443</v>
       </c>
       <c r="CK33" s="0">
         <v>1.316872427983538</v>
@@ -12079,7 +12080,7 @@
         <v>0.79250720461095037</v>
       </c>
       <c r="DB33" s="0">
-        <v>3.5788923719958174</v>
+        <v>3.5788923719958175</v>
       </c>
       <c r="DC33" s="0">
         <v>4.1311180960933953</v>
@@ -12153,7 +12154,7 @@
         <v>1.3233665559246943</v>
       </c>
       <c r="J34" s="0">
-        <v>1.1126031076155753</v>
+        <v>1.1126031076155754</v>
       </c>
       <c r="K34" s="0">
         <v>1.1592550361079428</v>
@@ -12177,7 +12178,7 @@
         <v>1.1316872427983529</v>
       </c>
       <c r="R34" s="0">
-        <v>1.377410468319558</v>
+        <v>1.3774104683195581</v>
       </c>
       <c r="S34" s="0">
         <v>1.1934615027398523</v>
@@ -12339,7 +12340,7 @@
         <v>1.3611212084494515</v>
       </c>
       <c r="BT34" s="0">
-        <v>1.2210633426608994</v>
+        <v>1.2210633426608995</v>
       </c>
       <c r="BU34" s="0">
         <v>1.233032846337166</v>
@@ -12438,7 +12439,7 @@
         <v>3.0684378155830005</v>
       </c>
       <c r="DA34" s="0">
-        <v>1.4649375600384233</v>
+        <v>1.4649375600384234</v>
       </c>
       <c r="DB34" s="0">
         <v>3.7617554858934139</v>
@@ -12740,7 +12741,7 @@
         <v>1.2089810017271145</v>
       </c>
       <c r="CG35" s="0">
-        <v>1.1109141405188196</v>
+        <v>1.1109141405188197</v>
       </c>
       <c r="CH35" s="0">
         <v>1.0732741486683439</v>
@@ -12809,7 +12810,7 @@
         <v>3.0309833857206976</v>
       </c>
       <c r="DD35" s="0">
-        <v>2.0157862780813582</v>
+        <v>2.0157862780813583</v>
       </c>
       <c r="DE35" s="0">
         <v>0.28999516674722065</v>
@@ -12856,7 +12857,7 @@
         <v>1.1038635223281477</v>
       </c>
       <c r="C36" s="0">
-        <v>1.1872146118721449</v>
+        <v>1.187214611872145</v>
       </c>
       <c r="D36" s="0">
         <v>1.2840477556484429</v>
@@ -13024,7 +13025,7 @@
         <v>0.84686935998889279</v>
       </c>
       <c r="BG36" s="0">
-        <v>1.2076401725200236</v>
+        <v>1.2076401725200237</v>
       </c>
       <c r="BH36" s="0">
         <v>1.221552878179383</v>
@@ -13111,7 +13112,7 @@
         <v>1.1536328341652791</v>
       </c>
       <c r="CJ36" s="0">
-        <v>1.1279780729496089</v>
+        <v>1.127978072949609</v>
       </c>
       <c r="CK36" s="0">
         <v>1.2090251170710931</v>
@@ -13162,7 +13163,7 @@
         <v>3.8607939097335473</v>
       </c>
       <c r="DA36" s="0">
-        <v>2.4735830931796325</v>
+        <v>2.4735830931796326</v>
       </c>
       <c r="DB36" s="0">
         <v>3.0303030303030276</v>
@@ -13204,7 +13205,7 @@
         <v>3.3203124999999969</v>
       </c>
       <c r="DO36" s="0">
-        <v>2.9126213592232983</v>
+        <v>2.9126213592232984</v>
       </c>
       <c r="DP36" s="0">
         <v>1.0563380281690131</v>
@@ -13233,7 +13234,7 @@
         <v>1.2954059829059819</v>
       </c>
       <c r="H37" s="0">
-        <v>1.3523059844585716</v>
+        <v>1.3523059844585717</v>
       </c>
       <c r="I37" s="0">
         <v>1.3565891472868206</v>
@@ -13383,7 +13384,7 @@
         <v>1.0782934833567737</v>
       </c>
       <c r="BF37" s="0">
-        <v>0.93016798556157076</v>
+        <v>0.93016798556157077</v>
       </c>
       <c r="BG37" s="0">
         <v>1.3000616142945152</v>
@@ -13431,7 +13432,7 @@
         <v>1.2952025696818972</v>
       </c>
       <c r="BV37" s="0">
-        <v>0.85176085176085103</v>
+        <v>0.85176085176085104</v>
       </c>
       <c r="BW37" s="0">
         <v>1.3011695906432739</v>
@@ -13589,7 +13590,7 @@
         <v>1.2833691555306441</v>
       </c>
       <c r="F38" s="0">
-        <v>1.2969498723135719</v>
+        <v>1.296949872313572</v>
       </c>
       <c r="G38" s="0">
         <v>1.2954059829059914</v>
@@ -13607,7 +13608,7 @@
         <v>1.3112884834663712</v>
       </c>
       <c r="L38" s="0">
-        <v>1.2253596164091713</v>
+        <v>1.2253596164091714</v>
       </c>
       <c r="M38" s="0">
         <v>1.2474012474012557</v>
@@ -13628,10 +13629,10 @@
         <v>1.6988062442608007</v>
       </c>
       <c r="S38" s="0">
-        <v>1.3002693415064634</v>
+        <v>1.3002693415064635</v>
       </c>
       <c r="T38" s="0">
-        <v>1.4068155432630018</v>
+        <v>1.4068155432630019</v>
       </c>
       <c r="U38" s="0">
         <v>1.1154489682097117</v>
@@ -13670,10 +13671,10 @@
         <v>1.4035087719298336</v>
       </c>
       <c r="AG38" s="0">
-        <v>0.96574618982949167</v>
+        <v>0.96574618982949168</v>
       </c>
       <c r="AH38" s="0">
-        <v>1.2527751347922695</v>
+        <v>1.2527751347922696</v>
       </c>
       <c r="AI38" s="0">
         <v>0.97294010337489234</v>
@@ -13700,7 +13701,7 @@
         <v>0.89771891096394996</v>
       </c>
       <c r="AQ38" s="0">
-        <v>1.2017167381974327</v>
+        <v>1.2017167381974328</v>
       </c>
       <c r="AR38" s="0">
         <v>1.1339563862928421</v>
@@ -13781,7 +13782,7 @@
         <v>1.2443168222062775</v>
       </c>
       <c r="BR38" s="0">
-        <v>1.2028739807863162</v>
+        <v>1.2028739807863163</v>
       </c>
       <c r="BS38" s="0">
         <v>1.0178117048346123</v>
@@ -13832,7 +13833,7 @@
         <v>1.2720286206439728</v>
       </c>
       <c r="CI38" s="0">
-        <v>1.2756516916250777</v>
+        <v>1.2756516916250778</v>
       </c>
       <c r="CJ38" s="0">
         <v>0.91714104996838042</v>
@@ -13916,7 +13917,7 @@
         <v>2.9810298102981223</v>
       </c>
       <c r="DK38" s="0">
-        <v>1.687471104946844</v>
+        <v>1.6874711049468441</v>
       </c>
       <c r="DL38" s="0">
         <v>3.8294168842471965</v>
@@ -13931,7 +13932,7 @@
         <v>2.1844660194174899</v>
       </c>
       <c r="DP38" s="0">
-        <v>1.173708920187801</v>
+        <v>1.1737089201878011</v>
       </c>
     </row>
     <row r="39">
@@ -14038,7 +14039,7 @@
         <v>1.2131303520456698</v>
       </c>
       <c r="AI39" s="0">
-        <v>0.90199655417046642</v>
+        <v>0.90199655417046643</v>
       </c>
       <c r="AJ39" s="0">
         <v>0.93911248710010242</v>
@@ -14101,7 +14102,7 @@
         <v>1.1300152361604867</v>
       </c>
       <c r="BD39" s="0">
-        <v>1.3155190133607388</v>
+        <v>1.3155190133607389</v>
       </c>
       <c r="BE39" s="0">
         <v>1.3439599937490221</v>
@@ -14221,7 +14222,7 @@
         <v>0.243823146944083</v>
       </c>
       <c r="CR39" s="0">
-        <v>3.2811334824757616</v>
+        <v>3.2811334824757617</v>
       </c>
       <c r="CS39" s="0">
         <v>3.4498009730207841</v>
@@ -14290,7 +14291,7 @@
         <v>3.2552083333333304</v>
       </c>
       <c r="DO39" s="0">
-        <v>1.7799352750809045</v>
+        <v>1.7799352750809046</v>
       </c>
       <c r="DP39" s="0">
         <v>0.70422535211267545</v>
@@ -14340,7 +14341,7 @@
         <v>1.2149532710280364</v>
       </c>
       <c r="O40" s="0">
-        <v>1.2392063805945543</v>
+        <v>1.2392063805945544</v>
       </c>
       <c r="P40" s="0">
         <v>1.3023943581868838</v>
@@ -14364,7 +14365,7 @@
         <v>0.88848039215686192</v>
       </c>
       <c r="W40" s="0">
-        <v>0.75213675213675157</v>
+        <v>0.75213675213675158</v>
       </c>
       <c r="X40" s="0">
         <v>0.9475080538184566</v>
@@ -14391,7 +14392,7 @@
         <v>0.88797814207650194</v>
       </c>
       <c r="AF40" s="0">
-        <v>1.684210526315788</v>
+        <v>1.6842105263157881</v>
       </c>
       <c r="AG40" s="0">
         <v>0.98083597404557021</v>
@@ -14418,7 +14419,7 @@
         <v>1.0430247718383303</v>
       </c>
       <c r="AO40" s="0">
-        <v>1.4232209737827703</v>
+        <v>1.4232209737827704</v>
       </c>
       <c r="AP40" s="0">
         <v>0.67696835908756381</v>
@@ -14526,7 +14527,7 @@
         <v>0.82737343991025036</v>
       </c>
       <c r="BY40" s="0">
-        <v>1.282051282051281</v>
+        <v>1.2820512820512811</v>
       </c>
       <c r="BZ40" s="0">
         <v>1.171669299631384</v>
@@ -14550,7 +14551,7 @@
         <v>1.2089810017271145</v>
       </c>
       <c r="CG40" s="0">
-        <v>1.2940967913490506</v>
+        <v>1.2940967913490507</v>
       </c>
       <c r="CH40" s="0">
         <v>1.3515304094342111</v>
@@ -14660,7 +14661,7 @@
     </row>
     <row r="41">
       <c r="A41" s="0">
-        <v>1.2116089039165951</v>
+        <v>1.2116089039165952</v>
       </c>
       <c r="B41" s="0">
         <v>0.97006188325806897</v>
@@ -14717,7 +14718,7 @@
         <v>1.2631187888919837</v>
       </c>
       <c r="T41" s="0">
-        <v>1.3453527282660644</v>
+        <v>1.3453527282660645</v>
       </c>
       <c r="U41" s="0">
         <v>1.3199479457148158</v>
@@ -14726,7 +14727,7 @@
         <v>1.3327205882352928</v>
       </c>
       <c r="W41" s="0">
-        <v>0.94017094017093938</v>
+        <v>0.94017094017093939</v>
       </c>
       <c r="X41" s="0">
         <v>1.2507106310403626</v>
@@ -14786,10 +14787,10 @@
         <v>0.69168506254598905</v>
       </c>
       <c r="AQ41" s="0">
-        <v>1.373390557939913</v>
+        <v>1.3733905579399131</v>
       </c>
       <c r="AR41" s="0">
-        <v>1.1713395638629271</v>
+        <v>1.1713395638629272</v>
       </c>
       <c r="AS41" s="0">
         <v>1.785714285714284</v>
@@ -14822,7 +14823,7 @@
         <v>1.0348905972797153</v>
       </c>
       <c r="BC41" s="0">
-        <v>1.1723379041814785</v>
+        <v>1.1723379041814786</v>
       </c>
       <c r="BD41" s="0">
         <v>1.3086673518328185</v>
@@ -14948,7 +14949,7 @@
         <v>2.3063811654415662</v>
       </c>
       <c r="CS41" s="0">
-        <v>2.1450685537372824</v>
+        <v>2.1450685537372825</v>
       </c>
       <c r="CT41" s="0">
         <v>0.53397410225604014</v>
@@ -14957,7 +14958,7 @@
         <v>0.39920159680638689</v>
       </c>
       <c r="CV41" s="0">
-        <v>0.87064676616915337</v>
+        <v>0.87064676616915338</v>
       </c>
       <c r="CW41" s="0">
         <v>0.41257128989200303</v>
@@ -14969,7 +14970,7 @@
         <v>0.27554907204797768</v>
       </c>
       <c r="CZ41" s="0">
-        <v>1.4526528392760027</v>
+        <v>1.4526528392760028</v>
       </c>
       <c r="DA41" s="0">
         <v>3.5542747358309286</v>
@@ -14993,10 +14994,10 @@
         <v>0</v>
       </c>
       <c r="DH41" s="0">
-        <v>2.7629233511586428</v>
+        <v>2.7629233511586429</v>
       </c>
       <c r="DI41" s="0">
-        <v>2.4922118380062281</v>
+        <v>2.4922118380062282</v>
       </c>
       <c r="DJ41" s="0">
         <v>0.88075880758807512</v>
@@ -15008,7 +15009,7 @@
         <v>2.3063533507397715</v>
       </c>
       <c r="DM41" s="0">
-        <v>1.282051282051281</v>
+        <v>1.2820512820512811</v>
       </c>
       <c r="DN41" s="0">
         <v>1.6276041666666652</v>
@@ -15040,7 +15041,7 @@
         <v>1.2051304123267614</v>
       </c>
       <c r="G42" s="0">
-        <v>1.282051282051281</v>
+        <v>1.2820512820512811</v>
       </c>
       <c r="H42" s="0">
         <v>1.2312039559995953</v>
@@ -15073,7 +15074,7 @@
         <v>1.3888888888888875</v>
       </c>
       <c r="R42" s="0">
-        <v>1.5610651974288325</v>
+        <v>1.5610651974288326</v>
       </c>
       <c r="S42" s="0">
         <v>1.0495031113587805</v>
@@ -15085,7 +15086,7 @@
         <v>1.2084030488938453</v>
       </c>
       <c r="V42" s="0">
-        <v>1.2254901960784303</v>
+        <v>1.2254901960784304</v>
       </c>
       <c r="W42" s="0">
         <v>0.97435897435897345</v>
@@ -15109,7 +15110,7 @@
         <v>1.1347517730496444</v>
       </c>
       <c r="AD42" s="0">
-        <v>0.80894599095883823</v>
+        <v>0.80894599095883824</v>
       </c>
       <c r="AE42" s="0">
         <v>0.95628415300546366</v>
@@ -15121,7 +15122,7 @@
         <v>1.2826316583672841</v>
       </c>
       <c r="AH42" s="0">
-        <v>0.9118300031715818</v>
+        <v>0.91183000317158181</v>
       </c>
       <c r="AI42" s="0">
         <v>0.88172696868348965</v>
@@ -15265,7 +15266,7 @@
         <v>1.5123109611298575</v>
       </c>
       <c r="CD42" s="0">
-        <v>1.282051282051281</v>
+        <v>1.2820512820512811</v>
       </c>
       <c r="CE42" s="0">
         <v>0.69841269841269771</v>
@@ -15370,7 +15371,7 @@
         <v>2.0017406440382923</v>
       </c>
       <c r="DM42" s="0">
-        <v>0.85470085470085388</v>
+        <v>0.85470085470085389</v>
       </c>
       <c r="DN42" s="0">
         <v>1.1067708333333324</v>
@@ -15414,7 +15415,7 @@
         <v>1.0422661295479241</v>
       </c>
       <c r="K43" s="0">
-        <v>1.0072215887495239</v>
+        <v>1.007221588749524</v>
       </c>
       <c r="L43" s="0">
         <v>0.95897709110282281</v>
@@ -15444,13 +15445,13 @@
         <v>1.2224270982722107</v>
       </c>
       <c r="U43" s="0">
-        <v>1.3571295779884724</v>
+        <v>1.3571295779884725</v>
       </c>
       <c r="V43" s="0">
         <v>1.531862745098038</v>
       </c>
       <c r="W43" s="0">
-        <v>0.75213675213675157</v>
+        <v>0.75213675213675158</v>
       </c>
       <c r="X43" s="0">
         <v>1.1370096645821479</v>
@@ -15531,7 +15532,7 @@
         <v>0.66379619662719713</v>
       </c>
       <c r="AX43" s="0">
-        <v>0.41527397954015965</v>
+        <v>0.41527397954015966</v>
       </c>
       <c r="AY43" s="0">
         <v>0.51904280417930526</v>
@@ -15564,7 +15565,7 @@
         <v>1.1601963409192315</v>
       </c>
       <c r="BI43" s="0">
-        <v>0.93957324726555413</v>
+        <v>0.93957324726555414</v>
       </c>
       <c r="BJ43" s="0">
         <v>1.1571770775750865</v>
@@ -15663,7 +15664,7 @@
         <v>1.309177466278761</v>
       </c>
       <c r="CP43" s="0">
-        <v>1.1552144541711626</v>
+        <v>1.1552144541711627</v>
       </c>
       <c r="CQ43" s="0">
         <v>0.0054182921543129555</v>
@@ -15696,13 +15697,13 @@
         <v>0.65252854812397976</v>
       </c>
       <c r="DA43" s="0">
-        <v>1.9932756964457234</v>
+        <v>1.9932756964457235</v>
       </c>
       <c r="DB43" s="0">
         <v>0.052246603970741851</v>
       </c>
       <c r="DC43" s="0">
-        <v>0.037419547971860471</v>
+        <v>0.037419547971860472</v>
       </c>
       <c r="DD43" s="0">
         <v>0.0060716454159077055</v>
@@ -15717,7 +15718,7 @@
         <v>0</v>
       </c>
       <c r="DH43" s="0">
-        <v>1.158645276292334</v>
+        <v>1.1586452762923341</v>
       </c>
       <c r="DI43" s="0">
         <v>1.8691588785046711</v>
@@ -15776,7 +15777,7 @@
         <v>0.97832342221369573</v>
       </c>
       <c r="K44" s="0">
-        <v>0.91220068415051236</v>
+        <v>0.91220068415051237</v>
       </c>
       <c r="L44" s="0">
         <v>1.1898419463683172</v>
@@ -15797,7 +15798,7 @@
         <v>0.77160493827160426</v>
       </c>
       <c r="R44" s="0">
-        <v>1.377410468319558</v>
+        <v>1.3774104683195581</v>
       </c>
       <c r="S44" s="0">
         <v>0.93340763443856145</v>
@@ -15896,7 +15897,7 @@
         <v>0.57733211789729522</v>
       </c>
       <c r="AY44" s="0">
-        <v>0.5325244354566897</v>
+        <v>0.53252443545668971</v>
       </c>
       <c r="AZ44" s="0">
         <v>1.2597258243793985</v>
@@ -15920,7 +15921,7 @@
         <v>1.1106483409690397</v>
       </c>
       <c r="BG44" s="0">
-        <v>0.90573012939001762</v>
+        <v>0.90573012939001763</v>
       </c>
       <c r="BH44" s="0">
         <v>0.98728246318607682</v>
@@ -15995,7 +15996,7 @@
         <v>0.44444444444444409</v>
       </c>
       <c r="CF44" s="0">
-        <v>1.4968336211859516</v>
+        <v>1.4968336211859517</v>
       </c>
       <c r="CG44" s="0">
         <v>1.2763694380428992</v>
@@ -16013,13 +16014,13 @@
         <v>0.81169291897261175</v>
       </c>
       <c r="CL44" s="0">
-        <v>1.2283693318176065</v>
+        <v>1.2283693318176066</v>
       </c>
       <c r="CM44" s="0">
         <v>0.55897149245388433</v>
       </c>
       <c r="CN44" s="0">
-        <v>0.57430007178750841</v>
+        <v>0.57430007178750842</v>
       </c>
       <c r="CO44" s="0">
         <v>1.1857533280437265</v>
@@ -16111,16 +16112,16 @@
         <v>0.83725798011512231</v>
       </c>
       <c r="B45" s="0">
-        <v>0.8571667502926904</v>
+        <v>0.85716675029269041</v>
       </c>
       <c r="C45" s="0">
-        <v>0.65399911621740991</v>
+        <v>0.65399911621740992</v>
       </c>
       <c r="D45" s="0">
         <v>1.029970221020134</v>
       </c>
       <c r="E45" s="0">
-        <v>0.940722050898669</v>
+        <v>0.94072205089866901</v>
       </c>
       <c r="F45" s="0">
         <v>1.0846173710940852</v>
@@ -16171,13 +16172,13 @@
         <v>1.1154489682097035</v>
       </c>
       <c r="V45" s="0">
-        <v>1.4093137254901948</v>
+        <v>1.4093137254901949</v>
       </c>
       <c r="W45" s="0">
         <v>0.70085470085470025</v>
       </c>
       <c r="X45" s="0">
-        <v>1.3644115974985775</v>
+        <v>1.3644115974985776</v>
       </c>
       <c r="Y45" s="0">
         <v>0.96960167714884615</v>
@@ -16252,10 +16253,10 @@
         <v>0.57381324986958737</v>
       </c>
       <c r="AW45" s="0">
-        <v>0.60100466451381362</v>
+        <v>0.60100466451381363</v>
       </c>
       <c r="AX45" s="0">
-        <v>0.41527397954015965</v>
+        <v>0.41527397954015966</v>
       </c>
       <c r="AY45" s="0">
         <v>0.40444893832153656</v>
@@ -16330,13 +16331,13 @@
         <v>0.31122031122031096</v>
       </c>
       <c r="BW45" s="0">
-        <v>0.97953216374268925</v>
+        <v>0.97953216374268926</v>
       </c>
       <c r="BX45" s="0">
         <v>1.1078390127611826</v>
       </c>
       <c r="BY45" s="0">
-        <v>0.64102564102564052</v>
+        <v>0.64102564102564053</v>
       </c>
       <c r="BZ45" s="0">
         <v>0.71090047393364875</v>
@@ -16381,7 +16382,7 @@
         <v>0.70803055710825347</v>
       </c>
       <c r="CN45" s="0">
-        <v>0.57430007178750841</v>
+        <v>0.57430007178750842</v>
       </c>
       <c r="CO45" s="0">
         <v>1.2298333774133816</v>
@@ -16497,7 +16498,7 @@
         <v>0.71428571428571896</v>
       </c>
       <c r="J46" s="0">
-        <v>0.92077498561289683</v>
+        <v>0.92077498561289684</v>
       </c>
       <c r="K46" s="0">
         <v>0.76016723679209919</v>
@@ -16536,7 +16537,7 @@
         <v>1.1182598039215759</v>
       </c>
       <c r="W46" s="0">
-        <v>0.5811965811965849</v>
+        <v>0.58119658119658491</v>
       </c>
       <c r="X46" s="0">
         <v>1.326511275345849</v>
@@ -16551,7 +16552,7 @@
         <v>0.70360598065084012</v>
       </c>
       <c r="AB46" s="0">
-        <v>0.73574494175353033</v>
+        <v>0.73574494175353034</v>
       </c>
       <c r="AC46" s="0">
         <v>0.70921985815603295</v>
@@ -16596,7 +16597,7 @@
         <v>0.52980132450331474</v>
       </c>
       <c r="AQ46" s="0">
-        <v>1.2017167381974327</v>
+        <v>1.2017167381974328</v>
       </c>
       <c r="AR46" s="0">
         <v>1.3084112149532796</v>
@@ -16686,7 +16687,7 @@
         <v>1.013312982277629</v>
       </c>
       <c r="BU46" s="0">
-        <v>0.40410320174075492</v>
+        <v>0.40410320174075493</v>
       </c>
       <c r="BV46" s="0">
         <v>0.36036036036036273</v>
@@ -16874,7 +16875,7 @@
         <v>0.6749740394600201</v>
       </c>
       <c r="O47" s="0">
-        <v>0.9096302155428112</v>
+        <v>0.90963021554281121</v>
       </c>
       <c r="P47" s="0">
         <v>0.9895922197577196</v>
@@ -16898,7 +16899,7 @@
         <v>1.1182598039215677</v>
       </c>
       <c r="W47" s="0">
-        <v>0.66666666666666607</v>
+        <v>0.66666666666666608</v>
       </c>
       <c r="X47" s="0">
         <v>1.269660792116732</v>
@@ -16976,10 +16977,10 @@
         <v>0.43967508756241114</v>
       </c>
       <c r="AW47" s="0">
-        <v>0.50233225690706806</v>
+        <v>0.50233225690706807</v>
       </c>
       <c r="AX47" s="0">
-        <v>0.31398764306694998</v>
+        <v>0.31398764306694999</v>
       </c>
       <c r="AY47" s="0">
         <v>0.26963262554769102</v>
@@ -17254,7 +17255,7 @@
         <v>0.85365020829065008</v>
       </c>
       <c r="U48" s="0">
-        <v>1.0968581520728748</v>
+        <v>1.0968581520728749</v>
       </c>
       <c r="V48" s="0">
         <v>1.087622549019607</v>
@@ -17329,7 +17330,7 @@
         <v>0.39682539682539647</v>
       </c>
       <c r="AT48" s="0">
-        <v>0.44518642181413431</v>
+        <v>0.44518642181413432</v>
       </c>
       <c r="AU48" s="0">
         <v>0.9953016815034611</v>
@@ -17356,13 +17357,13 @@
         <v>0.49280504632367389</v>
       </c>
       <c r="BC48" s="0">
-        <v>1.1723379041814785</v>
+        <v>1.1723379041814786</v>
       </c>
       <c r="BD48" s="0">
         <v>0.8564576909900643</v>
       </c>
       <c r="BE48" s="0">
-        <v>0.90639162369120096</v>
+        <v>0.90639162369120097</v>
       </c>
       <c r="BF48" s="0">
         <v>1.5965569901429946</v>
@@ -17559,7 +17560,7 @@
         <v>0.5474379100752722</v>
       </c>
       <c r="B49" s="0">
-        <v>0.53102525505937392</v>
+        <v>0.53102525505937393</v>
       </c>
       <c r="C49" s="0">
         <v>0.42126970098689021</v>
@@ -17583,7 +17584,7 @@
         <v>0.63122923588039814</v>
       </c>
       <c r="J49" s="0">
-        <v>0.60745571967517042</v>
+        <v>0.60745571967517043</v>
       </c>
       <c r="K49" s="0">
         <v>0.77917141771189591</v>
@@ -17598,7 +17599,7 @@
         <v>0.72689511941848317</v>
       </c>
       <c r="O49" s="0">
-        <v>0.73165908641486987</v>
+        <v>0.73165908641486988</v>
       </c>
       <c r="P49" s="0">
         <v>0.89290792242506878</v>
@@ -17661,7 +17662,7 @@
         <v>0.29390898956116318</v>
       </c>
       <c r="AJ49" s="0">
-        <v>0.25799793601651166</v>
+        <v>0.25799793601651167</v>
       </c>
       <c r="AK49" s="0">
         <v>0.52002080083203284</v>
@@ -17721,7 +17722,7 @@
         <v>1.2019637717961731</v>
       </c>
       <c r="BD49" s="0">
-        <v>0.79479273723877963</v>
+        <v>0.79479273723877964</v>
       </c>
       <c r="BE49" s="0">
         <v>0.67197999687451104</v>
@@ -17757,7 +17758,7 @@
         <v>1.249577845322525</v>
       </c>
       <c r="BP49" s="0">
-        <v>0.27189888300999387</v>
+        <v>0.27189888300999388</v>
       </c>
       <c r="BQ49" s="0">
         <v>0.76573342905001129</v>
@@ -17960,7 +17961,7 @@
         <v>0.53997923156801619</v>
       </c>
       <c r="O50" s="0">
-        <v>0.62619471359831202</v>
+        <v>0.62619471359831203</v>
       </c>
       <c r="P50" s="0">
         <v>0.78484900187681206</v>
@@ -18017,7 +18018,7 @@
         <v>1.2977214425833701</v>
       </c>
       <c r="AH50" s="0">
-        <v>0.38851887091658704</v>
+        <v>0.38851887091658705</v>
       </c>
       <c r="AI50" s="0">
         <v>0.19256106212627935</v>
@@ -18197,7 +18198,7 @@
         <v>0.789032883716829</v>
       </c>
       <c r="CP50" s="0">
-        <v>0.89539113402885961</v>
+        <v>0.89539113402885962</v>
       </c>
       <c r="CQ50" s="0">
         <v>0</v>
@@ -18316,7 +18317,7 @@
         <v>0.35517670040845289</v>
       </c>
       <c r="M51" s="0">
-        <v>0.44352044352044317</v>
+        <v>0.44352044352044318</v>
       </c>
       <c r="N51" s="0">
         <v>0.52959501557632349</v>
@@ -18376,7 +18377,7 @@
         <v>0.49122807017543813</v>
       </c>
       <c r="AG51" s="0">
-        <v>1.1468236004225127</v>
+        <v>1.1468236004225128</v>
       </c>
       <c r="AH51" s="0">
         <v>0.36473200126863276</v>
@@ -18454,7 +18455,7 @@
         <v>1.2217131750659438</v>
       </c>
       <c r="BG51" s="0">
-        <v>0.30807147258163869</v>
+        <v>0.3080714725816387</v>
       </c>
       <c r="BH51" s="0">
         <v>0.50200803212851364</v>
@@ -18463,7 +18464,7 @@
         <v>0.28689259458490202</v>
       </c>
       <c r="BJ51" s="0">
-        <v>0.45697438732264561</v>
+        <v>0.45697438732264562</v>
       </c>
       <c r="BK51" s="0">
         <v>0.66625455044989301</v>
@@ -18484,13 +18485,13 @@
         <v>0.13962375073486172</v>
       </c>
       <c r="BQ51" s="0">
-        <v>0.58626465661641491</v>
+        <v>0.58626465661641492</v>
       </c>
       <c r="BR51" s="0">
         <v>0.24218939210462562</v>
       </c>
       <c r="BS51" s="0">
-        <v>0.27868653822852268</v>
+        <v>0.27868653822852269</v>
       </c>
       <c r="BT51" s="0">
         <v>0.64021029424234654</v>
@@ -18505,7 +18506,7 @@
         <v>0.3362573099415202</v>
       </c>
       <c r="BX51" s="0">
-        <v>0.77128032534006385</v>
+        <v>0.77128032534006386</v>
       </c>
       <c r="BY51" s="0">
         <v>0.36231884057970981</v>
@@ -18849,7 +18850,7 @@
         <v>0.68198133524766635</v>
       </c>
       <c r="BR52" s="0">
-        <v>0.17760555421005877</v>
+        <v>0.17760555421005878</v>
       </c>
       <c r="BS52" s="0">
         <v>0.25849186154529641</v>
@@ -18885,7 +18886,7 @@
         <v>0.51243594550681115</v>
       </c>
       <c r="CD52" s="0">
-        <v>0.85897435897435825</v>
+        <v>0.85897435897435826</v>
       </c>
       <c r="CE52" s="0">
         <v>0.063492063492063433</v>
@@ -19016,7 +19017,7 @@
         <v>0.33603802966969887</v>
       </c>
       <c r="E53" s="0">
-        <v>0.38625673613057931</v>
+        <v>0.38625673613057932</v>
       </c>
       <c r="F53" s="0">
         <v>0.54230868554704259</v>
@@ -19058,7 +19059,7 @@
         <v>0.50505050505050464</v>
       </c>
       <c r="S53" s="0">
-        <v>0.36221788799108356</v>
+        <v>0.36221788799108357</v>
       </c>
       <c r="T53" s="0">
         <v>0.48487331830908925</v>
@@ -19070,7 +19071,7 @@
         <v>0.59742647058823473</v>
       </c>
       <c r="W53" s="0">
-        <v>0.20512820512820495</v>
+        <v>0.20512820512820496</v>
       </c>
       <c r="X53" s="0">
         <v>0.70115595982565782</v>
@@ -19091,7 +19092,7 @@
         <v>0.28368794326241109</v>
       </c>
       <c r="AD53" s="0">
-        <v>0.071377587437544548</v>
+        <v>0.071377587437544549</v>
       </c>
       <c r="AE53" s="0">
         <v>0.20491803278688506</v>
@@ -19130,7 +19131,7 @@
         <v>0.029433406916850598</v>
       </c>
       <c r="AQ53" s="0">
-        <v>0.75822603719599357</v>
+        <v>0.75822603719599358</v>
       </c>
       <c r="AR53" s="0">
         <v>0.73520249221183742</v>
@@ -19181,7 +19182,7 @@
         <v>0.33271719038816977</v>
       </c>
       <c r="BH53" s="0">
-        <v>0.44065149486836191</v>
+        <v>0.44065149486836192</v>
       </c>
       <c r="BI53" s="0">
         <v>0.19006634391249758</v>
@@ -19208,7 +19209,7 @@
         <v>0.095532039976484337</v>
       </c>
       <c r="BQ53" s="0">
-        <v>0.57430007178750841</v>
+        <v>0.57430007178750842</v>
       </c>
       <c r="BR53" s="0">
         <v>0.09687575684185025</v>
@@ -19220,7 +19221,7 @@
         <v>0.53845501568727172</v>
       </c>
       <c r="BU53" s="0">
-        <v>0.15542430836182763</v>
+        <v>0.15542430836182764</v>
       </c>
       <c r="BV53" s="0">
         <v>0.13104013104013093</v>
@@ -19256,7 +19257,7 @@
         <v>0.63327576280944098</v>
       </c>
       <c r="CG53" s="0">
-        <v>0.59682089464042964</v>
+        <v>0.59682089464042965</v>
       </c>
       <c r="CH53" s="0">
         <v>0.4372598383463624</v>
@@ -19378,7 +19379,7 @@
         <v>0.34969811217659724</v>
       </c>
       <c r="E54" s="0">
-        <v>0.33018720991807587</v>
+        <v>0.33018720991807588</v>
       </c>
       <c r="F54" s="0">
         <v>0.38736334681931617</v>
@@ -19390,7 +19391,7 @@
         <v>0.36330608537692971</v>
       </c>
       <c r="I54" s="0">
-        <v>0.24916943521594664</v>
+        <v>0.24916943521594665</v>
       </c>
       <c r="J54" s="0">
         <v>0.30053072447087381</v>
@@ -19462,7 +19463,7 @@
         <v>0.21052631578947351</v>
       </c>
       <c r="AG54" s="0">
-        <v>0.82993813188471321</v>
+        <v>0.82993813188471322</v>
       </c>
       <c r="AH54" s="0">
         <v>0.17443704408499827</v>
@@ -19570,7 +19571,7 @@
         <v>0.095532039976484337</v>
       </c>
       <c r="BQ54" s="0">
-        <v>0.57430007178750841</v>
+        <v>0.57430007178750842</v>
       </c>
       <c r="BR54" s="0">
         <v>0.13724065552595452</v>
@@ -19621,7 +19622,7 @@
         <v>0.66182119009631801</v>
       </c>
       <c r="CH54" s="0">
-        <v>0.43284307230245977</v>
+        <v>0.43284307230245978</v>
       </c>
       <c r="CI54" s="0">
         <v>0.68774265113699318</v>
@@ -19642,10 +19643,10 @@
         <v>0.10768126346015784</v>
       </c>
       <c r="CO54" s="0">
-        <v>0.50692056775103544</v>
+        <v>0.50692056775103545</v>
       </c>
       <c r="CP54" s="0">
-        <v>0.57161130431306661</v>
+        <v>0.57161130431306662</v>
       </c>
       <c r="CQ54" s="0">
         <v>0</v>
@@ -19767,7 +19768,7 @@
         <v>0.26334026334026506</v>
       </c>
       <c r="N55" s="0">
-        <v>0.29075804776739544</v>
+        <v>0.29075804776739545</v>
       </c>
       <c r="O55" s="0">
         <v>0.38230835146002495</v>
@@ -19914,7 +19915,7 @@
         <v>0.26902524414962403</v>
       </c>
       <c r="BK55" s="0">
-        <v>0.4121162167731327</v>
+        <v>0.41211621677313271</v>
       </c>
       <c r="BL55" s="0">
         <v>0.64959877722583537</v>
@@ -20123,7 +20124,7 @@
         <v>0.19004180919802341</v>
       </c>
       <c r="L56" s="0">
-        <v>0.23086485526549438</v>
+        <v>0.23086485526549439</v>
       </c>
       <c r="M56" s="0">
         <v>0.18018018018018003</v>
@@ -20153,7 +20154,7 @@
         <v>0.74363264547313557</v>
       </c>
       <c r="V56" s="0">
-        <v>0.49019607843137208</v>
+        <v>0.49019607843137209</v>
       </c>
       <c r="W56" s="0">
         <v>0.15384615384615372</v>
@@ -20345,7 +20346,7 @@
         <v>0.51409324587838989</v>
       </c>
       <c r="CH56" s="0">
-        <v>0.37984187977562794</v>
+        <v>0.37984187977562795</v>
       </c>
       <c r="CI56" s="0">
         <v>0.43261231281197965</v>
@@ -20464,7 +20465,7 @@
         <v>0.16392099008277994</v>
       </c>
       <c r="E57" s="0">
-        <v>0.20870323645765176</v>
+        <v>0.20870323645765177</v>
       </c>
       <c r="F57" s="0">
         <v>0.23241800809158969</v>
@@ -20880,7 +20881,7 @@
         <v>0.47487745098039175</v>
       </c>
       <c r="W58" s="0">
-        <v>0.085470085470085388</v>
+        <v>0.085470085470085389</v>
       </c>
       <c r="X58" s="0">
         <v>0.49270418798559745</v>
@@ -21051,7 +21052,7 @@
         <v>0.15037593984962394</v>
       </c>
       <c r="CB58" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC58" s="0">
         <v>0.27496562929633772</v>
@@ -21072,7 +21073,7 @@
         <v>0.29592332494147761</v>
       </c>
       <c r="CI58" s="0">
-        <v>0.26622296173044901</v>
+        <v>0.26622296173044902</v>
       </c>
       <c r="CJ58" s="0">
         <v>0.010541851149061766</v>
@@ -21081,7 +21082,7 @@
         <v>0.11919965942954439</v>
       </c>
       <c r="CL58" s="0">
-        <v>0.64102564102564052</v>
+        <v>0.64102564102564053</v>
       </c>
       <c r="CM58" s="0">
         <v>0.074529532327184581</v>
@@ -21413,7 +21414,7 @@
         <v>0.30075187969924788</v>
       </c>
       <c r="CB59" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC59" s="0">
         <v>0.1749781277340331</v>
@@ -21434,10 +21435,10 @@
         <v>0.23850536637074313</v>
       </c>
       <c r="CI59" s="0">
-        <v>0.26622296173044901</v>
+        <v>0.26622296173044902</v>
       </c>
       <c r="CJ59" s="0">
-        <v>0.031625553447185296</v>
+        <v>0.031625553447185297</v>
       </c>
       <c r="CK59" s="0">
         <v>0.11352348517099466</v>
@@ -21580,7 +21581,7 @@
         <v>0.14537902388369664</v>
       </c>
       <c r="O60" s="0">
-        <v>0.098872849515522956</v>
+        <v>0.098872849515522957</v>
       </c>
       <c r="P60" s="0">
         <v>0.21043052948871049</v>
@@ -21700,7 +21701,7 @@
         <v>0.04928050463236739</v>
       </c>
       <c r="BC60" s="0">
-        <v>0.52480108346030085</v>
+        <v>0.52480108346030086</v>
       </c>
       <c r="BD60" s="0">
         <v>0.1370332305584103</v>
@@ -21739,7 +21740,7 @@
         <v>0.46155578070471642</v>
       </c>
       <c r="BP60" s="0">
-        <v>0.02204585537918869</v>
+        <v>0.022045855379188691</v>
       </c>
       <c r="BQ60" s="0">
         <v>0.23929169657812852</v>
@@ -21936,7 +21937,7 @@
         <v>0.035517670040845287</v>
       </c>
       <c r="M61" s="0">
-        <v>0.027720027720027698</v>
+        <v>0.027720027720027699</v>
       </c>
       <c r="N61" s="0">
         <v>0.051921079958463089</v>
@@ -21963,7 +21964,7 @@
         <v>0.50195203569436653</v>
       </c>
       <c r="V61" s="0">
-        <v>0.29105392156862719</v>
+        <v>0.2910539215686272</v>
       </c>
       <c r="W61" s="0">
         <v>0.051282051282051239</v>
@@ -22137,7 +22138,7 @@
         <v>0.40100250626566381</v>
       </c>
       <c r="CB61" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC61" s="0">
         <v>0.13748281464816886</v>
@@ -22164,7 +22165,7 @@
         <v>0.010541851149061766</v>
       </c>
       <c r="CK61" s="0">
-        <v>0.087980701007520853</v>
+        <v>0.087980701007520854</v>
       </c>
       <c r="CL61" s="0">
         <v>0.41998231653404033</v>
@@ -22457,7 +22458,7 @@
         <v>0.24335129497653377</v>
       </c>
       <c r="BN62" s="0">
-        <v>0.031046258925799416</v>
+        <v>0.031046258925799417</v>
       </c>
       <c r="BO62" s="0">
         <v>0.45029832263874775</v>
@@ -22645,13 +22646,13 @@
         <v>0.040064102564102824</v>
       </c>
       <c r="H63" s="0">
-        <v>0.04036734281965916</v>
+        <v>0.040367342819659161</v>
       </c>
       <c r="I63" s="0">
         <v>0.066445182724252913</v>
       </c>
       <c r="J63" s="0">
-        <v>0.04475989513396026</v>
+        <v>0.044759895133960261</v>
       </c>
       <c r="K63" s="0">
         <v>0.01900418091980248</v>
@@ -22711,7 +22712,7 @@
         <v>0.047281323877068869</v>
       </c>
       <c r="AD63" s="0">
-        <v>0.023792529145848357</v>
+        <v>0.023792529145848358</v>
       </c>
       <c r="AE63" s="0">
         <v>0</v>
@@ -23013,7 +23014,7 @@
         <v>0.07751937984496117</v>
       </c>
       <c r="J64" s="0">
-        <v>0.044759895133959927</v>
+        <v>0.044759895133959928</v>
       </c>
       <c r="K64" s="0">
         <v>0.038008361839604682</v>
@@ -23025,7 +23026,7 @@
         <v>0.055440055440055397</v>
       </c>
       <c r="N64" s="0">
-        <v>0.041536863966770476</v>
+        <v>0.041536863966770477</v>
       </c>
       <c r="O64" s="0">
         <v>0.052732186408278911</v>
@@ -23127,7 +23128,7 @@
         <v>0.14836795252225507</v>
       </c>
       <c r="AV64" s="0">
-        <v>0.0074521201281764603</v>
+        <v>0.0074521201281764604</v>
       </c>
       <c r="AW64" s="0">
         <v>0.0089702188733405009</v>
@@ -23175,19 +23176,19 @@
         <v>0.082423243354625933</v>
       </c>
       <c r="BL64" s="0">
-        <v>0.18468984842695182</v>
+        <v>0.18468984842695183</v>
       </c>
       <c r="BM64" s="0">
-        <v>0.092705255229155722</v>
+        <v>0.092705255229155723</v>
       </c>
       <c r="BN64" s="0">
-        <v>0.031046258925799416</v>
+        <v>0.031046258925799417</v>
       </c>
       <c r="BO64" s="0">
         <v>0.34898120004502953</v>
       </c>
       <c r="BP64" s="0">
-        <v>0.02204585537918869</v>
+        <v>0.022045855379188691</v>
       </c>
       <c r="BQ64" s="0">
         <v>0.059822924144532129</v>
@@ -23241,7 +23242,7 @@
         <v>0.088636766530756889</v>
       </c>
       <c r="CH64" s="0">
-        <v>0.075085022746345056</v>
+        <v>0.075085022746345057</v>
       </c>
       <c r="CI64" s="0">
         <v>0.14420410427065988</v>
@@ -23265,7 +23266,7 @@
         <v>0.11020012342413814</v>
       </c>
       <c r="CP64" s="0">
-        <v>0.13191030099532305</v>
+        <v>0.13191030099532306</v>
       </c>
       <c r="CQ64" s="0">
         <v>0</v>
@@ -23363,7 +23364,7 @@
         <v>0.052954552534031037</v>
       </c>
       <c r="F65" s="0">
-        <v>0.068864594990100655</v>
+        <v>0.068864594990100656</v>
       </c>
       <c r="G65" s="0">
         <v>0</v>
@@ -23519,7 +23520,7 @@
         <v>0.04688232536333798</v>
       </c>
       <c r="BF65" s="0">
-        <v>0.29154518950437291</v>
+        <v>0.29154518950437292</v>
       </c>
       <c r="BG65" s="0">
         <v>0.0061614294516327732</v>
@@ -23624,7 +23625,7 @@
         <v>0.011964584828906426</v>
       </c>
       <c r="CO65" s="0">
-        <v>0.070528078991448417</v>
+        <v>0.070528078991448418</v>
       </c>
       <c r="CP65" s="0">
         <v>0.079945636966862466</v>
@@ -23746,10 +23747,10 @@
         <v>0.05327650506126793</v>
       </c>
       <c r="M66" s="0">
-        <v>0.027720027720027698</v>
+        <v>0.027720027720027699</v>
       </c>
       <c r="N66" s="0">
-        <v>0.041536863966770476</v>
+        <v>0.041536863966770477</v>
       </c>
       <c r="O66" s="0">
         <v>0.0065915233010348639</v>
@@ -23851,7 +23852,7 @@
         <v>0.1112759643916913</v>
       </c>
       <c r="AV66" s="0">
-        <v>0.0074521201281764603</v>
+        <v>0.0074521201281764604</v>
       </c>
       <c r="AW66" s="0">
         <v>0.0089702188733405009</v>
@@ -23878,7 +23879,7 @@
         <v>0.041109969167523089</v>
       </c>
       <c r="BE66" s="0">
-        <v>0.031254883575558653</v>
+        <v>0.031254883575558654</v>
       </c>
       <c r="BF66" s="0">
         <v>0.15271414688324297</v>
@@ -23941,7 +23942,7 @@
         <v>0</v>
       </c>
       <c r="BZ66" s="0">
-        <v>0.026329647182727726</v>
+        <v>0.026329647182727727</v>
       </c>
       <c r="CA66" s="0">
         <v>0.050125313283207976</v>
@@ -23950,7 +23951,7 @@
         <v>0</v>
       </c>
       <c r="CC66" s="0">
-        <v>0.074990626171728469</v>
+        <v>0.07499062617172847</v>
       </c>
       <c r="CD66" s="0">
         <v>0.19230769230769215</v>
@@ -23974,7 +23975,7 @@
         <v>0</v>
       </c>
       <c r="CK66" s="0">
-        <v>0.017028522775649198</v>
+        <v>0.017028522775649199</v>
       </c>
       <c r="CL66" s="0">
         <v>0.21788556271314871</v>
@@ -24135,7 +24136,7 @@
         <v>0.09295408068414264</v>
       </c>
       <c r="V67" s="0">
-        <v>0.061274509803921968</v>
+        <v>0.061274509803921969</v>
       </c>
       <c r="W67" s="0">
         <v>0</v>
@@ -24210,7 +24211,7 @@
         <v>0</v>
       </c>
       <c r="AU67" s="0">
-        <v>0.068001978239367405</v>
+        <v>0.068001978239367406</v>
       </c>
       <c r="AV67" s="0">
         <v>0</v>
@@ -24883,7 +24884,7 @@
         <v>0</v>
       </c>
       <c r="AD69" s="0">
-        <v>0.023792529145848357</v>
+        <v>0.023792529145848358</v>
       </c>
       <c r="AE69" s="0">
         <v>0.068306010928962199</v>
@@ -25072,7 +25073,7 @@
         <v>0</v>
       </c>
       <c r="CO69" s="0">
-        <v>0.035264039495724465</v>
+        <v>0.035264039495724466</v>
       </c>
       <c r="CP69" s="0">
         <v>0.07195107327017676</v>
@@ -25296,7 +25297,7 @@
         <v>0</v>
       </c>
       <c r="AU70" s="0">
-        <v>0.030909990108802909</v>
+        <v>0.03090999010880291</v>
       </c>
       <c r="AV70" s="0">
         <v>0.0074521201281764048</v>
@@ -25673,7 +25674,7 @@
         <v>0.0067408156386923254</v>
       </c>
       <c r="AZ71" s="0">
-        <v>0.098802025441522195</v>
+        <v>0.098802025441522196</v>
       </c>
       <c r="BA71" s="0">
         <v>0</v>
@@ -25730,7 +25731,7 @@
         <v>0</v>
       </c>
       <c r="BS71" s="0">
-        <v>0.0040389353366452867</v>
+        <v>0.0040389353366452868</v>
       </c>
       <c r="BT71" s="0">
         <v>0.012719409819384464</v>
@@ -25897,7 +25898,7 @@
         <v>0</v>
       </c>
       <c r="F72" s="0">
-        <v>0.017216148747525035</v>
+        <v>0.017216148747525036</v>
       </c>
       <c r="G72" s="0">
         <v>0</v>
@@ -26080,7 +26081,7 @@
         <v>0</v>
       </c>
       <c r="BO72" s="0">
-        <v>0.022514916131937224</v>
+        <v>0.022514916131937225</v>
       </c>
       <c r="BP72" s="0">
         <v>0</v>
@@ -26134,10 +26135,10 @@
         <v>0</v>
       </c>
       <c r="CG72" s="0">
-        <v>0.017727353306151244</v>
+        <v>0.017727353306151245</v>
       </c>
       <c r="CH72" s="0">
-        <v>0.0088335320878052351</v>
+        <v>0.0088335320878052352</v>
       </c>
       <c r="CI72" s="0">
         <v>0.011092623405435294</v>
@@ -26289,7 +26290,7 @@
         <v>0</v>
       </c>
       <c r="P73" s="0">
-        <v>0.0056873116078030288</v>
+        <v>0.0056873116078030289</v>
       </c>
       <c r="Q73" s="0">
         <v>0</v>
@@ -26436,7 +26437,7 @@
         <v>0.025474461851993542</v>
       </c>
       <c r="BM73" s="0">
-        <v>0.017382235355466825</v>
+        <v>0.017382235355466826</v>
       </c>
       <c r="BN73" s="0">
         <v>0</v>
@@ -26858,10 +26859,10 @@
         <v>0.057570523891766937</v>
       </c>
       <c r="CG74" s="0">
-        <v>0.017727353306151244</v>
+        <v>0.017727353306151245</v>
       </c>
       <c r="CH74" s="0">
-        <v>0.0088335320878052351</v>
+        <v>0.0088335320878052352</v>
       </c>
       <c r="CI74" s="0">
         <v>0</v>
@@ -27139,7 +27140,7 @@
         <v>0.015627441787779445</v>
       </c>
       <c r="BF75" s="0">
-        <v>0.055532417048452395</v>
+        <v>0.055532417048452396</v>
       </c>
       <c r="BG75" s="0">
         <v>0</v>
@@ -27160,7 +27161,7 @@
         <v>0.0063686154629983855</v>
       </c>
       <c r="BM75" s="0">
-        <v>0.017382235355466825</v>
+        <v>0.017382235355466826</v>
       </c>
       <c r="BN75" s="0">
         <v>0</v>
@@ -27178,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="BS75" s="0">
-        <v>0.0040389353366452867</v>
+        <v>0.0040389353366452868</v>
       </c>
       <c r="BT75" s="0">
         <v>0.0042398032731281541</v>
@@ -27492,7 +27493,7 @@
         <v>0</v>
       </c>
       <c r="BC76" s="0">
-        <v>0.033858134416793854</v>
+        <v>0.033858134416793855</v>
       </c>
       <c r="BD76" s="0">
         <v>0</v>
@@ -28099,7 +28100,7 @@
         <v>0</v>
       </c>
       <c r="P78" s="0">
-        <v>0.0056873116078030288</v>
+        <v>0.0056873116078030289</v>
       </c>
       <c r="Q78" s="0">
         <v>0</v>

--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0005_ses-01_pet_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0005_ses-01_pet_pdf.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
